--- a/runs/RELX/2026-10-14/bear/scratch/b_tax_25/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_tax_25/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1985.141584374865</v>
+        <v>2041.411352562063</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.0958361764</v>
+        <v>0.089050626976</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10803.85999244605</v>
+        <v>10967.86650756636</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>36885.03136459611</v>
+        <v>40509.69364923039</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>24434.01331634671</v>
+        <v>27595.77826307584</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>35237.87330879275</v>
+        <v>38563.6447706422</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>28240.87330879275</v>
+        <v>31566.6447706422</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>27225.6401177459</v>
+        <v>30628.71019763233</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>15.6132279937016</v>
+        <v>17.56480411114168</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1561.322799370161</v>
+        <v>1756.480411114168</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4365489717</v>
+        <v>-0.3661203857</v>
       </c>
     </row>
   </sheetData>
